--- a/이자영.xlsx
+++ b/이자영.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ahn\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{802B39FE-F713-428F-B27E-E14FE1F0492A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{578F8F9F-0414-4671-AAC1-C1D4428D11B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
+    <workbookView xWindow="36060" yWindow="3840" windowWidth="21600" windowHeight="11295" xr2:uid="{515CDDB1-FDC0-43BD-B4BB-9EBEF2D25055}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,21 +30,6 @@
     <t>교시</t>
   </si>
   <si>
-    <t>월(24)</t>
-  </si>
-  <si>
-    <t>화(25)</t>
-  </si>
-  <si>
-    <t>수(26)</t>
-  </si>
-  <si>
-    <t>목(27)</t>
-  </si>
-  <si>
-    <t>금(28)</t>
-  </si>
-  <si>
     <t>1(08:20)</t>
   </si>
   <si>
@@ -69,10 +54,25 @@
     <t>8(16:00)</t>
   </si>
   <si>
+    <t>생명</t>
+  </si>
+  <si>
     <t>통과C</t>
   </si>
   <si>
-    <t>생명</t>
+    <t>월(7)</t>
+  </si>
+  <si>
+    <t>화(8)</t>
+  </si>
+  <si>
+    <t>수(9)</t>
+  </si>
+  <si>
+    <t>목(10)</t>
+  </si>
+  <si>
+    <t>금(11)</t>
   </si>
   <si>
     <t>동아리</t>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -216,7 +216,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -541,24 +541,24 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="7" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2">
         <v>204</v>
@@ -572,27 +572,31 @@
       <c r="E2" s="2">
         <v>101</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="2">
+        <v>107</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="8"/>
       <c r="B3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="6"/>
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B4" s="2">
         <v>204</v>
@@ -603,35 +607,31 @@
       <c r="D4" s="2">
         <v>207</v>
       </c>
-      <c r="E4" s="2">
-        <v>107</v>
-      </c>
-      <c r="F4" s="5"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="8"/>
       <c r="B5" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>14</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+        <v>3</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
       <c r="F6" s="2">
         <v>209</v>
       </c>
@@ -643,16 +643,16 @@
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
       <c r="E8" s="2">
         <v>109</v>
       </c>
@@ -666,15 +666,15 @@
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>207</v>
@@ -685,74 +685,74 @@
       <c r="D10" s="2">
         <v>204</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="9"/>
+      <c r="F10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="8"/>
       <c r="B11" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B12" s="2">
         <v>207</v>
       </c>
-      <c r="C12" s="5"/>
+      <c r="C12" s="9"/>
       <c r="D12" s="2">
         <v>204</v>
       </c>
       <c r="E12" s="2">
         <v>103</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="3" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" s="6"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5"/>
+        <v>7</v>
+      </c>
+      <c r="B14" s="9"/>
       <c r="C14" s="2">
         <v>105</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
     </row>
     <row r="15" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8"/>
       <c r="B15" s="6"/>
       <c r="C15" s="3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -760,7 +760,7 @@
     </row>
     <row r="16" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -770,29 +770,29 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="F12:F13"/>
     <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="F14:F15"/>
     <mergeCell ref="C12:C13"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
